--- a/downloads/timbulan_data/Data_Timbulan_Sampah_SIPSN_KLHK_Jawa Timur_2024.xlsx
+++ b/downloads/timbulan_data/Data_Timbulan_Sampah_SIPSN_KLHK_Jawa Timur_2024.xlsx
@@ -451,6 +451,594 @@
         <v>306270.96</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C13">
+        <is>
+          <t xml:space="preserve">Kab. Bondowoso</t>
+        </is>
+      </c>
+      <c r="D13" s="66">
+        <v>315.20</v>
+      </c>
+      <c r="E13" s="64">
+        <v>115049.02</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
+          <t xml:space="preserve">Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="D14" s="66">
+        <v>256.63</v>
+      </c>
+      <c r="E14" s="64">
+        <v>93669.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C15">
+        <is>
+          <t xml:space="preserve">Kab. Probolinggo</t>
+        </is>
+      </c>
+      <c r="D15" s="66">
+        <v>465.54</v>
+      </c>
+      <c r="E15" s="64">
+        <v>169923.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">Kab. Pasuruan</t>
+        </is>
+      </c>
+      <c r="D16" s="66">
+        <v>671.39</v>
+      </c>
+      <c r="E16" s="64">
+        <v>245057.20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B17">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">Kab. Sidoarjo</t>
+        </is>
+      </c>
+      <c r="D17" s="66">
+        <v>878.60</v>
+      </c>
+      <c r="E17" s="64">
+        <v>320690.10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C18">
+        <is>
+          <t xml:space="preserve">Kab. Mojokerto</t>
+        </is>
+      </c>
+      <c r="D18" s="66">
+        <v>449.64</v>
+      </c>
+      <c r="E18" s="64">
+        <v>164117.17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C19">
+        <is>
+          <t xml:space="preserve">Kab. Jombang</t>
+        </is>
+      </c>
+      <c r="D19" s="66">
+        <v>530.37</v>
+      </c>
+      <c r="E19" s="64">
+        <v>193583.44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">Kab. Nganjuk</t>
+        </is>
+      </c>
+      <c r="D20" s="66">
+        <v>457.80</v>
+      </c>
+      <c r="E20" s="64">
+        <v>167098.17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">Kab. Madiun</t>
+        </is>
+      </c>
+      <c r="D21" s="66">
+        <v>295.69</v>
+      </c>
+      <c r="E21" s="64">
+        <v>107927.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">Kab. Magetan</t>
+        </is>
+      </c>
+      <c r="D22" s="66">
+        <v>276.65</v>
+      </c>
+      <c r="E22" s="64">
+        <v>100976.23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">Kab. Ngawi</t>
+        </is>
+      </c>
+      <c r="D23" s="66">
+        <v>371.87</v>
+      </c>
+      <c r="E23" s="64">
+        <v>135732.55</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Kab. Bojonegoro</t>
+        </is>
+      </c>
+      <c r="D24" s="66">
+        <v>368.03</v>
+      </c>
+      <c r="E24" s="64">
+        <v>134329.37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Kab. Tuban</t>
+        </is>
+      </c>
+      <c r="D25" s="66">
+        <v>528.51</v>
+      </c>
+      <c r="E25" s="64">
+        <v>192907.81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">Kab. Lamongan</t>
+        </is>
+      </c>
+      <c r="D26" s="66">
+        <v>554.33</v>
+      </c>
+      <c r="E26" s="64">
+        <v>202331.91</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">Kab. Gresik</t>
+        </is>
+      </c>
+      <c r="D27" s="66">
+        <v>402.23</v>
+      </c>
+      <c r="E27" s="64">
+        <v>146814.53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">Kab. Bangkalan</t>
+        </is>
+      </c>
+      <c r="D28" s="66">
+        <v>417.67</v>
+      </c>
+      <c r="E28" s="64">
+        <v>152450.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">Kab. Sampang</t>
+        </is>
+      </c>
+      <c r="D29" s="66">
+        <v>464.41</v>
+      </c>
+      <c r="E29" s="64">
+        <v>169511.29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">Kab. Pamekasan</t>
+        </is>
+      </c>
+      <c r="D30" s="66">
+        <v>280.74</v>
+      </c>
+      <c r="E30" s="64">
+        <v>102470.10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">Kab. Sumenep</t>
+        </is>
+      </c>
+      <c r="D31" s="66">
+        <v>364.55</v>
+      </c>
+      <c r="E31" s="64">
+        <v>133059.91</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">Kota Kediri</t>
+        </is>
+      </c>
+      <c r="D32" s="66">
+        <v>182.28</v>
+      </c>
+      <c r="E32" s="64">
+        <v>66532.27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C33">
+        <is>
+          <t xml:space="preserve">Kota Blitar</t>
+        </is>
+      </c>
+      <c r="D33" s="66">
+        <v>77.44</v>
+      </c>
+      <c r="E33" s="64">
+        <v>28263.78</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C34">
+        <is>
+          <t xml:space="preserve">Kota Malang</t>
+        </is>
+      </c>
+      <c r="D34" s="66">
+        <v>731.24</v>
+      </c>
+      <c r="E34" s="64">
+        <v>266901.57</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="D35" s="66">
+        <v>121.87</v>
+      </c>
+      <c r="E35" s="64">
+        <v>44483.65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C36">
+        <is>
+          <t xml:space="preserve">Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="D36" s="66">
+        <v>148.87</v>
+      </c>
+      <c r="E36" s="64">
+        <v>54335.88</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B37">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C37">
+        <is>
+          <t xml:space="preserve">Kota Mojokerto</t>
+        </is>
+      </c>
+      <c r="D37" s="66">
+        <v>99.25</v>
+      </c>
+      <c r="E37" s="64">
+        <v>36226.07</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C38">
+        <is>
+          <t xml:space="preserve">Kota Madiun</t>
+        </is>
+      </c>
+      <c r="D38" s="66">
+        <v>124.08</v>
+      </c>
+      <c r="E38" s="64">
+        <v>45287.39</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B39">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="D39" s="64">
+        <v>1810.81</v>
+      </c>
+      <c r="E39" s="64">
+        <v>660946.82</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65">
+        <v>2024</v>
+      </c>
+      <c t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">Kota Batu</t>
+        </is>
+      </c>
+      <c r="D40" s="66">
+        <v>144.96</v>
+      </c>
+      <c r="E40" s="64">
+        <v>52910.59</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
